--- a/datos_p.xlsx
+++ b/datos_p.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Avances_Tesis_FCB\Script_analisis_GLM\Script GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7FF686-3852-4002-BFB2-DE1C806E0ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2947426A-AD2A-4CF7-99B9-7D215F0F0CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="598" xr2:uid="{721657E2-12F1-4ED3-8AA7-95A02CEC2D7D}"/>
   </bookViews>
   <sheets>
-    <sheet name="con_patrones" sheetId="1" r:id="rId1"/>
+    <sheet name="con_pa" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,23 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>sample</t>
   </si>
   <si>
-    <t>T_den</t>
-  </si>
-  <si>
-    <t>T_fue</t>
-  </si>
-  <si>
-    <t>H_den</t>
-  </si>
-  <si>
-    <t>H_fue</t>
-  </si>
-  <si>
     <t>Pen</t>
   </si>
   <si>
@@ -111,25 +99,22 @@
   </si>
   <si>
     <t>P15</t>
+  </si>
+  <si>
+    <t>V_hu</t>
+  </si>
+  <si>
+    <t>V_te</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -155,10 +140,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,524 +476,427 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F0F897-8FD2-4EFD-A210-2F198F65C1C6}">
-  <dimension ref="A1:J16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{529D2D47-91AB-42E4-9581-B1E032F09EFC}">
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>23.5</v>
+        <v>0.14000000000000057</v>
       </c>
       <c r="D2" s="1">
-        <v>23.64</v>
+        <v>0.10000000000001563</v>
       </c>
       <c r="E2" s="1">
-        <v>60.739999999999995</v>
+        <v>14.86</v>
       </c>
       <c r="F2" s="1">
-        <v>60.840000000000011</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1">
-        <v>14.86</v>
-      </c>
-      <c r="H2" s="2">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1">
         <v>1.4339999999999999</v>
       </c>
-      <c r="J2" s="2">
+      <c r="H2">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>29.216666666666669</v>
+        <v>2.3333333333336981E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>29.240000000000006</v>
+        <v>0.56666666666666288</v>
       </c>
       <c r="E3" s="1">
-        <v>48.906666666666673</v>
+        <v>10.393333333333333</v>
       </c>
       <c r="F3" s="1">
-        <v>49.473333333333336</v>
+        <v>34</v>
       </c>
       <c r="G3" s="1">
-        <v>10.393333333333333</v>
-      </c>
-      <c r="H3" s="2">
-        <v>34</v>
-      </c>
-      <c r="I3" s="1">
         <v>2.254</v>
       </c>
-      <c r="J3" s="2">
+      <c r="H3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>28.259999999999998</v>
+        <v>0.16000000000000725</v>
       </c>
       <c r="D4" s="1">
-        <v>28.420000000000005</v>
+        <v>0.39999999999999858</v>
       </c>
       <c r="E4" s="1">
-        <v>50.86</v>
+        <v>16.02</v>
       </c>
       <c r="F4" s="1">
-        <v>50.46</v>
+        <v>20.6</v>
       </c>
       <c r="G4" s="1">
-        <v>16.02</v>
-      </c>
-      <c r="H4" s="2">
-        <v>20.6</v>
-      </c>
-      <c r="I4" s="1">
         <v>2.0140000000000002</v>
       </c>
-      <c r="J4" s="2">
+      <c r="H4">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" s="1">
-        <v>25.98</v>
+        <v>5.9999999999998721E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>26.04</v>
+        <v>0.57999999999999119</v>
       </c>
       <c r="E5" s="1">
-        <v>54.820000000000007</v>
+        <v>20.04</v>
       </c>
       <c r="F5" s="1">
-        <v>55.4</v>
+        <v>34</v>
       </c>
       <c r="G5" s="1">
-        <v>20.04</v>
-      </c>
-      <c r="H5" s="2">
-        <v>34</v>
-      </c>
-      <c r="I5" s="1">
         <v>2.742</v>
       </c>
-      <c r="J5" s="2">
+      <c r="H5">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>32.040000000000006</v>
+        <v>0.13999999999998636</v>
       </c>
       <c r="D6" s="1">
-        <v>32.179999999999993</v>
+        <v>1.3399999999999963</v>
       </c>
       <c r="E6" s="1">
-        <v>51.160000000000004</v>
+        <v>11.04</v>
       </c>
       <c r="F6" s="1">
-        <v>52.5</v>
+        <v>22.2</v>
       </c>
       <c r="G6" s="1">
-        <v>11.04</v>
-      </c>
-      <c r="H6" s="2">
-        <v>22.2</v>
-      </c>
-      <c r="I6" s="1">
         <v>1.21</v>
       </c>
-      <c r="J6" s="2">
+      <c r="H6">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>29.179999999999996</v>
+        <v>1.9999999999992468E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>29.160000000000004</v>
+        <v>2.279999999999994</v>
       </c>
       <c r="E7" s="1">
-        <v>50.56</v>
+        <v>9.36</v>
       </c>
       <c r="F7" s="1">
-        <v>48.280000000000008</v>
+        <v>22.2</v>
       </c>
       <c r="G7" s="1">
-        <v>9.36</v>
-      </c>
-      <c r="H7" s="2">
-        <v>22.2</v>
-      </c>
-      <c r="I7" s="1">
         <v>1.5779999999999998</v>
       </c>
-      <c r="J7" s="2">
+      <c r="H7">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
       <c r="C8" s="1">
-        <v>32.6</v>
+        <v>4.9999999999997158E-2</v>
       </c>
       <c r="D8" s="1">
-        <v>32.65</v>
+        <v>0.27499999999999858</v>
       </c>
       <c r="E8" s="1">
-        <v>40.774999999999999</v>
+        <v>9.125</v>
       </c>
       <c r="F8" s="1">
-        <v>41.05</v>
+        <v>15.5</v>
       </c>
       <c r="G8" s="1">
-        <v>9.125</v>
-      </c>
-      <c r="H8" s="2">
-        <v>15.5</v>
-      </c>
-      <c r="I8" s="1">
         <v>1.7674999999999998</v>
       </c>
-      <c r="J8" s="2">
+      <c r="H8">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
       <c r="C9" s="1">
-        <v>30.339999999999996</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="D9" s="1">
-        <v>30.46</v>
+        <v>1.5999999999999943</v>
       </c>
       <c r="E9" s="1">
-        <v>46.5</v>
+        <v>8.16</v>
       </c>
       <c r="F9" s="1">
-        <v>44.900000000000006</v>
+        <v>28.2</v>
       </c>
       <c r="G9" s="1">
-        <v>8.16</v>
-      </c>
-      <c r="H9" s="2">
-        <v>28.2</v>
-      </c>
-      <c r="I9" s="1">
         <v>1.92</v>
       </c>
-      <c r="J9" s="2">
+      <c r="H9">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>9</v>
       </c>
       <c r="C10" s="1">
-        <v>31.674999999999997</v>
+        <v>0.15000000000000213</v>
       </c>
       <c r="D10" s="1">
-        <v>31.824999999999999</v>
+        <v>2.4999999999998579E-2</v>
       </c>
       <c r="E10" s="1">
-        <v>51.949999999999996</v>
+        <v>10.074999999999999</v>
       </c>
       <c r="F10" s="1">
-        <v>51.974999999999994</v>
+        <v>34.25</v>
       </c>
       <c r="G10" s="1">
-        <v>10.074999999999999</v>
-      </c>
-      <c r="H10" s="2">
-        <v>34.25</v>
-      </c>
-      <c r="I10" s="1">
         <v>2.1124999999999998</v>
       </c>
-      <c r="J10" s="2">
+      <c r="H10">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
       <c r="C11" s="1">
-        <v>33.75</v>
+        <v>2.4999999999998579E-2</v>
       </c>
       <c r="D11" s="1">
-        <v>33.725000000000001</v>
+        <v>2.25</v>
       </c>
       <c r="E11" s="1">
-        <v>46.924999999999997</v>
+        <v>6.3999999999999995</v>
       </c>
       <c r="F11" s="1">
-        <v>49.174999999999997</v>
+        <v>33</v>
       </c>
       <c r="G11" s="1">
-        <v>6.3999999999999995</v>
-      </c>
-      <c r="H11" s="2">
-        <v>33</v>
-      </c>
-      <c r="I11" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="J11" s="2">
+      <c r="H11">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>11</v>
       </c>
       <c r="C12" s="1">
-        <v>29.5</v>
+        <v>1.8200000000000038</v>
       </c>
       <c r="D12" s="1">
-        <v>31.320000000000004</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="E12" s="1">
-        <v>48.18</v>
+        <v>15.16</v>
       </c>
       <c r="F12" s="1">
-        <v>47.62</v>
+        <v>25.6</v>
       </c>
       <c r="G12" s="1">
-        <v>15.16</v>
-      </c>
-      <c r="H12" s="2">
-        <v>25.6</v>
-      </c>
-      <c r="I12" s="1">
         <v>1.988</v>
       </c>
-      <c r="J12" s="2">
+      <c r="H12">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
       <c r="C13" s="1">
-        <v>23.54</v>
+        <v>8.0000000000001847E-2</v>
       </c>
       <c r="D13" s="1">
-        <v>23.62</v>
+        <v>1.9999999999988916E-2</v>
       </c>
       <c r="E13" s="1">
-        <v>62.260000000000005</v>
+        <v>15.859999999999996</v>
       </c>
       <c r="F13" s="1">
-        <v>62.279999999999994</v>
+        <v>23.4</v>
       </c>
       <c r="G13" s="1">
-        <v>15.859999999999996</v>
-      </c>
-      <c r="H13" s="2">
-        <v>23.4</v>
-      </c>
-      <c r="I13" s="1">
         <v>1.8560000000000003</v>
       </c>
-      <c r="J13" s="2">
+      <c r="H13">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>13</v>
       </c>
       <c r="C14" s="1">
-        <v>29.7</v>
+        <v>9.9999999999997868E-2</v>
       </c>
       <c r="D14" s="1">
-        <v>29.6</v>
+        <v>0.5</v>
       </c>
       <c r="E14" s="1">
-        <v>47.4</v>
+        <v>13.5</v>
       </c>
       <c r="F14" s="1">
-        <v>46.9</v>
+        <v>22</v>
       </c>
       <c r="G14" s="1">
-        <v>13.5</v>
-      </c>
-      <c r="H14" s="2">
-        <v>22</v>
-      </c>
-      <c r="I14" s="1">
         <v>1.95</v>
       </c>
-      <c r="J14" s="2">
+      <c r="H14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>14</v>
       </c>
       <c r="C15" s="1">
-        <v>33.059999999999995</v>
+        <v>0.69999999999999574</v>
       </c>
       <c r="D15" s="1">
-        <v>32.36</v>
+        <v>0.67999999999999261</v>
       </c>
       <c r="E15" s="1">
-        <v>49.320000000000007</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="F15" s="1">
-        <v>50</v>
+        <v>21.2</v>
       </c>
       <c r="G15" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="H15" s="2">
-        <v>21.2</v>
-      </c>
-      <c r="I15" s="1">
         <v>1.304</v>
       </c>
-      <c r="J15" s="2">
+      <c r="H15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>15</v>
       </c>
       <c r="C16" s="1">
-        <v>24.18</v>
+        <v>0.30000000000000071</v>
       </c>
       <c r="D16" s="1">
-        <v>24.48</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="E16" s="1">
-        <v>58.820000000000007</v>
+        <v>22.32</v>
       </c>
       <c r="F16" s="1">
-        <v>57.86</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1">
-        <v>22.32</v>
-      </c>
-      <c r="H16" s="2">
-        <v>30</v>
-      </c>
-      <c r="I16" s="1">
         <v>2.0379999999999998</v>
       </c>
-      <c r="J16" s="2">
+      <c r="H16">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datos_p.xlsx
+++ b/datos_p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Avances_Tesis_FCB\Script_analisis_GLM\Script GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2947426A-AD2A-4CF7-99B9-7D215F0F0CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3816ED2A-385A-4DCD-A9BF-95CA22870E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="598" xr2:uid="{721657E2-12F1-4ED3-8AA7-95A02CEC2D7D}"/>
   </bookViews>
@@ -523,7 +523,7 @@
         <v>14.86</v>
       </c>
       <c r="F2" s="1">
-        <v>18</v>
+        <v>0.18</v>
       </c>
       <c r="G2" s="1">
         <v>1.4339999999999999</v>
@@ -549,7 +549,7 @@
         <v>10.393333333333333</v>
       </c>
       <c r="F3" s="1">
-        <v>34</v>
+        <v>0.34</v>
       </c>
       <c r="G3" s="1">
         <v>2.254</v>
@@ -575,7 +575,7 @@
         <v>16.02</v>
       </c>
       <c r="F4" s="1">
-        <v>20.6</v>
+        <v>0.20600000000000002</v>
       </c>
       <c r="G4" s="1">
         <v>2.0140000000000002</v>
@@ -601,7 +601,7 @@
         <v>20.04</v>
       </c>
       <c r="F5" s="1">
-        <v>34</v>
+        <v>0.34</v>
       </c>
       <c r="G5" s="1">
         <v>2.742</v>
@@ -627,7 +627,7 @@
         <v>11.04</v>
       </c>
       <c r="F6" s="1">
-        <v>22.2</v>
+        <v>0.222</v>
       </c>
       <c r="G6" s="1">
         <v>1.21</v>
@@ -653,7 +653,7 @@
         <v>9.36</v>
       </c>
       <c r="F7" s="1">
-        <v>22.2</v>
+        <v>0.222</v>
       </c>
       <c r="G7" s="1">
         <v>1.5779999999999998</v>
@@ -679,7 +679,7 @@
         <v>9.125</v>
       </c>
       <c r="F8" s="1">
-        <v>15.5</v>
+        <v>0.155</v>
       </c>
       <c r="G8" s="1">
         <v>1.7674999999999998</v>
@@ -705,7 +705,7 @@
         <v>8.16</v>
       </c>
       <c r="F9" s="1">
-        <v>28.2</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="G9" s="1">
         <v>1.92</v>
@@ -731,7 +731,7 @@
         <v>10.074999999999999</v>
       </c>
       <c r="F10" s="1">
-        <v>34.25</v>
+        <v>0.34250000000000003</v>
       </c>
       <c r="G10" s="1">
         <v>2.1124999999999998</v>
@@ -757,7 +757,7 @@
         <v>6.3999999999999995</v>
       </c>
       <c r="F11" s="1">
-        <v>33</v>
+        <v>0.33</v>
       </c>
       <c r="G11" s="1">
         <v>2.4500000000000002</v>
@@ -783,7 +783,7 @@
         <v>15.16</v>
       </c>
       <c r="F12" s="1">
-        <v>25.6</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="G12" s="1">
         <v>1.988</v>
@@ -809,7 +809,7 @@
         <v>15.859999999999996</v>
       </c>
       <c r="F13" s="1">
-        <v>23.4</v>
+        <v>0.23399999999999999</v>
       </c>
       <c r="G13" s="1">
         <v>1.8560000000000003</v>
@@ -835,7 +835,7 @@
         <v>13.5</v>
       </c>
       <c r="F14" s="1">
-        <v>22</v>
+        <v>0.22</v>
       </c>
       <c r="G14" s="1">
         <v>1.95</v>
@@ -861,7 +861,7 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="F15" s="1">
-        <v>21.2</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="G15" s="1">
         <v>1.304</v>
@@ -887,7 +887,7 @@
         <v>22.32</v>
       </c>
       <c r="F16" s="1">
-        <v>30</v>
+        <v>0.3</v>
       </c>
       <c r="G16" s="1">
         <v>2.0379999999999998</v>

--- a/datos_p.xlsx
+++ b/datos_p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Avances_Tesis_FCB\Script_analisis_GLM\Script GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3816ED2A-385A-4DCD-A9BF-95CA22870E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343487C0-C14A-4F6E-9370-830F1AEF6974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="598" xr2:uid="{721657E2-12F1-4ED3-8AA7-95A02CEC2D7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>sample</t>
   </si>
@@ -50,9 +50,6 @@
     <t>T_par</t>
   </si>
   <si>
-    <t>Gru</t>
-  </si>
-  <si>
     <t>N_par</t>
   </si>
   <si>
@@ -105,12 +102,27 @@
   </si>
   <si>
     <t>V_te</t>
+  </si>
+  <si>
+    <t>T_den</t>
+  </si>
+  <si>
+    <t>T_fue</t>
+  </si>
+  <si>
+    <t>H_den</t>
+  </si>
+  <si>
+    <t>H_fue</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -140,9 +152,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,422 +490,566 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{529D2D47-91AB-42E4-9581-B1E032F09EFC}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>23.64</v>
+      </c>
+      <c r="D2" s="2">
+        <v>60.739999999999995</v>
+      </c>
+      <c r="E2" s="2">
+        <v>60.840000000000011</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.14000000000000057</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.10000000000001563</v>
+      </c>
+      <c r="H2" s="1">
+        <v>14.86</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.4339999999999999</v>
+      </c>
+      <c r="K2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>29.216666666666669</v>
+      </c>
+      <c r="C3" s="2">
+        <v>29.240000000000006</v>
+      </c>
+      <c r="D3" s="2">
+        <v>48.906666666666673</v>
+      </c>
+      <c r="E3" s="2">
+        <v>49.473333333333336</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2.3333333333336981E-2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.56666666666666288</v>
+      </c>
+      <c r="H3" s="1">
+        <v>10.393333333333333</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2.254</v>
+      </c>
+      <c r="K3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2">
+        <v>28.259999999999998</v>
+      </c>
+      <c r="C4" s="2">
+        <v>28.420000000000005</v>
+      </c>
+      <c r="D4" s="2">
+        <v>50.86</v>
+      </c>
+      <c r="E4" s="2">
+        <v>50.46</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.16000000000000725</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.39999999999999858</v>
+      </c>
+      <c r="H4" s="1">
+        <v>16.02</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.20600000000000002</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2.0140000000000002</v>
+      </c>
+      <c r="K4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2">
+        <v>25.98</v>
+      </c>
+      <c r="C5" s="2">
+        <v>26.04</v>
+      </c>
+      <c r="D5" s="2">
+        <v>54.820000000000007</v>
+      </c>
+      <c r="E5" s="2">
+        <v>55.4</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5.9999999999998721E-2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.57999999999999119</v>
+      </c>
+      <c r="H5" s="1">
+        <v>20.04</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2.742</v>
+      </c>
+      <c r="K5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2">
+        <v>32.040000000000006</v>
+      </c>
+      <c r="C6" s="2">
+        <v>32.179999999999993</v>
+      </c>
+      <c r="D6" s="2">
+        <v>51.160000000000004</v>
+      </c>
+      <c r="E6" s="2">
+        <v>52.5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.13999999999998636</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.3399999999999963</v>
+      </c>
+      <c r="H6" s="1">
+        <v>11.04</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.222</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.21</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2">
+        <v>29.179999999999996</v>
+      </c>
+      <c r="C7" s="2">
+        <v>29.160000000000004</v>
+      </c>
+      <c r="D7" s="2">
+        <v>50.56</v>
+      </c>
+      <c r="E7" s="2">
+        <v>48.280000000000008</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1.9999999999992468E-2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2.279999999999994</v>
+      </c>
+      <c r="H7" s="1">
+        <v>9.36</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.222</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1.5779999999999998</v>
+      </c>
+      <c r="K7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2">
+        <v>32.6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>32.65</v>
+      </c>
+      <c r="D8" s="2">
+        <v>40.774999999999999</v>
+      </c>
+      <c r="E8" s="2">
+        <v>41.05</v>
+      </c>
+      <c r="F8" s="1">
+        <v>4.9999999999997158E-2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.27499999999999858</v>
+      </c>
+      <c r="H8" s="1">
+        <v>9.125</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.155</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1.7674999999999998</v>
+      </c>
+      <c r="K8">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2">
+        <v>30.339999999999996</v>
+      </c>
+      <c r="C9" s="2">
+        <v>30.46</v>
+      </c>
+      <c r="D9" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="E9" s="2">
+        <v>44.900000000000006</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.12000000000000455</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.5999999999999943</v>
+      </c>
+      <c r="H9" s="1">
+        <v>8.16</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1.92</v>
+      </c>
+      <c r="K9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2">
+        <v>31.674999999999997</v>
+      </c>
+      <c r="C10" s="2">
+        <v>31.824999999999999</v>
+      </c>
+      <c r="D10" s="2">
+        <v>51.949999999999996</v>
+      </c>
+      <c r="E10" s="2">
+        <v>51.974999999999994</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.15000000000000213</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2.4999999999998579E-2</v>
+      </c>
+      <c r="H10" s="1">
+        <v>10.074999999999999</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.34250000000000003</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2.1124999999999998</v>
+      </c>
+      <c r="K10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2">
+        <v>33.75</v>
+      </c>
+      <c r="C11" s="2">
+        <v>33.725000000000001</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46.924999999999997</v>
+      </c>
+      <c r="E11" s="2">
+        <v>49.174999999999997</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2.4999999999998579E-2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="H11" s="1">
+        <v>6.3999999999999995</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="K11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="C12" s="2">
+        <v>31.320000000000004</v>
+      </c>
+      <c r="D12" s="2">
+        <v>48.18</v>
+      </c>
+      <c r="E12" s="2">
+        <v>47.62</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1.8200000000000038</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.56000000000000227</v>
+      </c>
+      <c r="H12" s="1">
+        <v>15.16</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1.988</v>
+      </c>
+      <c r="K12">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2">
+        <v>23.54</v>
+      </c>
+      <c r="C13" s="2">
+        <v>23.62</v>
+      </c>
+      <c r="D13" s="2">
+        <v>62.260000000000005</v>
+      </c>
+      <c r="E13" s="2">
+        <v>62.279999999999994</v>
+      </c>
+      <c r="F13" s="1">
+        <v>8.0000000000001847E-2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1.9999999999988916E-2</v>
+      </c>
+      <c r="H13" s="1">
+        <v>15.859999999999996</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.23399999999999999</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1.8560000000000003</v>
+      </c>
+      <c r="K13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2">
+        <v>29.7</v>
+      </c>
+      <c r="C14" s="2">
+        <v>29.6</v>
+      </c>
+      <c r="D14" s="2">
+        <v>47.4</v>
+      </c>
+      <c r="E14" s="2">
+        <v>46.9</v>
+      </c>
+      <c r="F14" s="1">
+        <v>9.9999999999997868E-2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1.95</v>
+      </c>
+      <c r="K14">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.14000000000000057</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.10000000000001563</v>
-      </c>
-      <c r="E2" s="1">
-        <v>14.86</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.4339999999999999</v>
-      </c>
-      <c r="H2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2.3333333333336981E-2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.56666666666666288</v>
-      </c>
-      <c r="E3" s="1">
-        <v>10.393333333333333</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2.254</v>
-      </c>
-      <c r="H3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.16000000000000725</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.39999999999999858</v>
-      </c>
-      <c r="E4" s="1">
-        <v>16.02</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.20600000000000002</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2.0140000000000002</v>
-      </c>
-      <c r="H4">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>33.059999999999995</v>
+      </c>
+      <c r="C15" s="2">
+        <v>32.36</v>
+      </c>
+      <c r="D15" s="2">
+        <v>49.320000000000007</v>
+      </c>
+      <c r="E15" s="2">
+        <v>50</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.69999999999999574</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.67999999999999261</v>
+      </c>
+      <c r="H15" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1.304</v>
+      </c>
+      <c r="K15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>5.9999999999998721E-2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.57999999999999119</v>
-      </c>
-      <c r="E5" s="1">
-        <v>20.04</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2.742</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.13999999999998636</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1.3399999999999963</v>
-      </c>
-      <c r="E6" s="1">
-        <v>11.04</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0.222</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.21</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.9999999999992468E-2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2.279999999999994</v>
-      </c>
-      <c r="E7" s="1">
-        <v>9.36</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0.222</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.5779999999999998</v>
-      </c>
-      <c r="H7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1">
-        <v>4.9999999999997158E-2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.27499999999999858</v>
-      </c>
-      <c r="E8" s="1">
-        <v>9.125</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0.155</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.7674999999999998</v>
-      </c>
-      <c r="H8">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.12000000000000455</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1.5999999999999943</v>
-      </c>
-      <c r="E9" s="1">
-        <v>8.16</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0.28199999999999997</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.92</v>
-      </c>
-      <c r="H9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.15000000000000213</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2.4999999999998579E-2</v>
-      </c>
-      <c r="E10" s="1">
-        <v>10.074999999999999</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.34250000000000003</v>
-      </c>
-      <c r="G10" s="1">
-        <v>2.1124999999999998</v>
-      </c>
-      <c r="H10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2.4999999999998579E-2</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2.25</v>
-      </c>
-      <c r="E11" s="1">
-        <v>6.3999999999999995</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="G11" s="1">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="H11">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1.8200000000000038</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0.56000000000000227</v>
-      </c>
-      <c r="E12" s="1">
-        <v>15.16</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0.25600000000000001</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.988</v>
-      </c>
-      <c r="H12">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13" s="1">
-        <v>8.0000000000001847E-2</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1.9999999999988916E-2</v>
-      </c>
-      <c r="E13" s="1">
-        <v>15.859999999999996</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0.23399999999999999</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1.8560000000000003</v>
-      </c>
-      <c r="H13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14">
-        <v>13</v>
-      </c>
-      <c r="C14" s="1">
-        <v>9.9999999999997868E-2</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E14" s="1">
-        <v>13.5</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1.95</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15">
-        <v>14</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.69999999999999574</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0.67999999999999261</v>
-      </c>
-      <c r="E15" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0.21199999999999999</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1.304</v>
-      </c>
-      <c r="H15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16">
-        <v>15</v>
-      </c>
-      <c r="C16" s="1">
+      <c r="B16" s="2">
+        <v>24.18</v>
+      </c>
+      <c r="C16" s="2">
+        <v>24.48</v>
+      </c>
+      <c r="D16" s="2">
+        <v>58.820000000000007</v>
+      </c>
+      <c r="E16" s="2">
+        <v>57.86</v>
+      </c>
+      <c r="F16" s="1">
         <v>0.30000000000000071</v>
       </c>
-      <c r="D16" s="1">
+      <c r="G16" s="1">
         <v>0.96000000000000796</v>
       </c>
-      <c r="E16" s="1">
+      <c r="H16" s="1">
         <v>22.32</v>
       </c>
-      <c r="F16" s="1">
+      <c r="I16" s="1">
         <v>0.3</v>
       </c>
-      <c r="G16" s="1">
+      <c r="J16" s="1">
         <v>2.0379999999999998</v>
       </c>
-      <c r="H16">
+      <c r="K16">
         <v>22</v>
       </c>
     </row>
